--- a/data/trans_orig/Q64C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que trabaja a la semana</t>
+          <t>Número medio de horas que trabaja a la semana (tasa de respuesta: 97,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,93; 43,76</t>
+          <t>42,01; 43,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,15; 44,65</t>
+          <t>42,04; 44,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 42,69</t>
+          <t>40,03; 42,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,33; 42,32</t>
+          <t>40,26; 42,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,59; 42,09</t>
+          <t>37,53; 42,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,88; 37,36</t>
+          <t>33,75; 37,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,09; 36,71</t>
+          <t>33,07; 36,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,01; 36,78</t>
+          <t>35,18; 36,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,97; 42,8</t>
+          <t>41,01; 42,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,21; 41,47</t>
+          <t>39,28; 41,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,57; 39,86</t>
+          <t>37,72; 39,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,31; 39,78</t>
+          <t>38,29; 39,67</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,82; 42,51</t>
+          <t>40,85; 42,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,86; 41,81</t>
+          <t>39,92; 41,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,96; 39,86</t>
+          <t>37,9; 39,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 40,11</t>
+          <t>16,63; 40,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,04; 38,04</t>
+          <t>34,91; 37,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,33; 36,45</t>
+          <t>33,13; 36,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 36,5</t>
+          <t>33,54; 36,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,45; 36,95</t>
+          <t>35,46; 36,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,23; 40,72</t>
+          <t>39,32; 40,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,49; 39,28</t>
+          <t>37,55; 39,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,49; 38,18</t>
+          <t>36,56; 38,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,03; 38,59</t>
+          <t>20,36; 38,57</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,4; 41,81</t>
+          <t>39,49; 41,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,1; 42,56</t>
+          <t>40,34; 42,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,75; 40,46</t>
+          <t>37,63; 40,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,82; 40,33</t>
+          <t>38,81; 40,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,58; 38,61</t>
+          <t>35,5; 38,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,94; 39,65</t>
+          <t>36,22; 39,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,07; 36,27</t>
+          <t>33,23; 36,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,17; 37,66</t>
+          <t>35,21; 37,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,5; 40,34</t>
+          <t>38,44; 40,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,94; 41,0</t>
+          <t>38,98; 41,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,1; 38,27</t>
+          <t>36,13; 38,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,35; 38,74</t>
+          <t>37,4; 38,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,99; 40,69</t>
+          <t>38,94; 40,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,44; 41,06</t>
+          <t>39,43; 41,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,26; 40,19</t>
+          <t>38,32; 40,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,61; 39,48</t>
+          <t>37,54; 39,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 37,89</t>
+          <t>35,51; 37,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,44; 36,6</t>
+          <t>34,39; 36,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,71; 36,11</t>
+          <t>33,79; 36,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,36; 34,55</t>
+          <t>27,46; 34,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,84; 39,17</t>
+          <t>37,82; 39,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,6; 38,97</t>
+          <t>37,56; 39,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,6; 38,15</t>
+          <t>36,51; 38,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 36,74</t>
+          <t>32,37; 36,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,69; 41,6</t>
+          <t>40,71; 41,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,75</t>
+          <t>40,76; 41,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,84; 40,02</t>
+          <t>38,88; 40,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,93; 39,89</t>
+          <t>25,59; 39,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,34; 37,83</t>
+          <t>36,41; 37,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,07; 36,69</t>
+          <t>35,06; 36,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,16; 35,67</t>
+          <t>34,18; 35,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,49; 35,82</t>
+          <t>32,33; 35,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,36; 40,13</t>
+          <t>39,34; 40,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,67; 39,51</t>
+          <t>38,59; 39,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36,99; 37,96</t>
+          <t>37,06; 38,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,16; 37,84</t>
+          <t>28,34; 37,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,28</t>
+          <t>41,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,04</t>
+          <t>36,03</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,0</t>
+          <t>38,9</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,01; 43,79</t>
+          <t>41,98; 43,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,04; 44,48</t>
+          <t>42,07; 44,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,03; 42,59</t>
+          <t>40,05; 42,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,26; 42,29</t>
+          <t>40,14; 42,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,53; 42,1</t>
+          <t>37,35; 41,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,75; 37,45</t>
+          <t>33,55; 37,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,07; 36,85</t>
+          <t>33,01; 36,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,18; 36,97</t>
+          <t>35,07; 36,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,01; 42,78</t>
+          <t>40,98; 42,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,28; 41,48</t>
+          <t>39,36; 41,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,72; 39,96</t>
+          <t>37,55; 39,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,29; 39,67</t>
+          <t>38,19; 39,59</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,12</t>
+          <t>40,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,25</t>
+          <t>36,28</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>38,57</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,85; 42,54</t>
+          <t>40,8; 42,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,92; 41,88</t>
+          <t>39,9; 41,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,9; 39,97</t>
+          <t>37,93; 39,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 40,13</t>
+          <t>39,38; 41,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,91; 37,83</t>
+          <t>35,11; 37,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,13; 36,26</t>
+          <t>33,3; 36,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,54; 36,39</t>
+          <t>33,56; 36,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,46; 36,99</t>
+          <t>35,49; 37,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,32; 40,82</t>
+          <t>39,22; 40,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,55; 39,2</t>
+          <t>37,51; 39,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,56; 38,22</t>
+          <t>36,47; 38,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 38,57</t>
+          <t>37,94; 39,17</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,63</t>
+          <t>39,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,39</t>
+          <t>35,99</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,08</t>
+          <t>38,06</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 41,89</t>
+          <t>39,43; 41,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,34; 42,62</t>
+          <t>40,14; 42,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,63; 40,47</t>
+          <t>37,53; 40,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,81; 40,4</t>
+          <t>38,99; 40,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,5; 38,48</t>
+          <t>35,49; 38,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,22; 39,63</t>
+          <t>36,14; 39,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,23; 36,3</t>
+          <t>33,07; 36,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,21; 37,69</t>
+          <t>34,85; 36,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,44; 40,3</t>
+          <t>38,41; 40,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,98; 41,01</t>
+          <t>38,97; 40,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,13; 38,17</t>
+          <t>36,18; 38,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,4; 38,68</t>
+          <t>37,42; 38,72</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,63</t>
+          <t>38,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>33,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,34</t>
+          <t>36,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,94; 40,68</t>
+          <t>38,92; 40,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,43; 41,11</t>
+          <t>39,43; 41,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,32; 40,14</t>
+          <t>38,27; 40,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37,54; 39,44</t>
+          <t>37,7; 39,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,51; 37,76</t>
+          <t>35,38; 37,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,39; 36,72</t>
+          <t>34,37; 36,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,79; 36,16</t>
+          <t>33,79; 36,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 34,55</t>
+          <t>33,02; 34,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,82; 39,29</t>
+          <t>37,86; 39,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,56; 39,01</t>
+          <t>37,55; 39,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,51; 38,05</t>
+          <t>36,52; 38,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,37; 36,82</t>
+          <t>35,81; 37,13</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,7</t>
+          <t>39,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,87</t>
+          <t>35,47</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,35</t>
+          <t>37,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,65</t>
+          <t>40,67; 41,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,76; 41,78</t>
+          <t>40,77; 41,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,88; 40,07</t>
+          <t>38,87; 40,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,59; 39,87</t>
+          <t>39,41; 40,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,41; 37,96</t>
+          <t>36,34; 37,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,06; 36,56</t>
+          <t>35,09; 36,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,18; 35,67</t>
+          <t>34,11; 35,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,33; 35,79</t>
+          <t>34,96; 35,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,34; 40,16</t>
+          <t>39,34; 40,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,51</t>
+          <t>38,6; 39,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,06; 38,02</t>
+          <t>37,05; 38,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,34; 37,75</t>
+          <t>37,6; 38,23</t>
         </is>
       </c>
     </row>
